--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2756559D-9B1E-4425-A29C-65126A745DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5F0ECB-B039-44E0-8083-2C00FE2D8104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -498,7 +498,7 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -539,7 +539,7 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>-7.5</v>
+        <v>-9</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -586,7 +586,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -627,7 +627,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1147,6 +1147,88 @@
       </c>
       <c r="M17">
         <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18">
+        <v>25</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>25</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0.5</v>
+      </c>
+      <c r="I18">
+        <v>0.5</v>
+      </c>
+      <c r="J18">
+        <v>0.5</v>
+      </c>
+      <c r="K18">
+        <v>-1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19">
+        <v>-25</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>25</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0.5</v>
+      </c>
+      <c r="I19">
+        <v>0.5</v>
+      </c>
+      <c r="J19">
+        <v>0.5</v>
+      </c>
+      <c r="K19">
+        <v>50</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5F0ECB-B039-44E0-8083-2C00FE2D8104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08FFE3C-EBC9-4964-895C-6BBE849BCDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -990,7 +990,7 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -1037,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1222,13 +1222,95 @@
         <v>0.5</v>
       </c>
       <c r="K19">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20">
+        <v>-25</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>-25</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0.5</v>
+      </c>
+      <c r="I20">
+        <v>0.5</v>
+      </c>
+      <c r="J20">
+        <v>0.5</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>-25</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0.5</v>
+      </c>
+      <c r="I21">
+        <v>0.5</v>
+      </c>
+      <c r="J21">
+        <v>0.5</v>
+      </c>
+      <c r="K21">
+        <v>-10</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08FFE3C-EBC9-4964-895C-6BBE849BCDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902E2F4C-1A49-46A5-8865-8AA8ECE91A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -501,7 +501,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D2">
         <v>-25</v>
@@ -542,7 +542,7 @@
         <v>-9</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -583,7 +583,7 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D4">
         <v>9</v>
@@ -624,7 +624,7 @@
         <v>-25</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D5">
         <v>-9</v>
@@ -955,7 +955,7 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>25</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D18">
         <v>25</v>
@@ -1198,7 +1198,7 @@
         <v>-25</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D19">
         <v>25</v>
@@ -1239,7 +1239,7 @@
         <v>-25</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D20">
         <v>-25</v>
@@ -1280,7 +1280,7 @@
         <v>25</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D21">
         <v>-25</v>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902E2F4C-1A49-46A5-8865-8AA8ECE91A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1419FEA-AD7A-4236-A51B-6BF4BC0C2B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33915" yWindow="-300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -501,7 +501,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="D2">
         <v>-25</v>
@@ -542,7 +542,7 @@
         <v>-9</v>
       </c>
       <c r="C3">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -583,7 +583,7 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="D4">
         <v>9</v>
@@ -624,7 +624,7 @@
         <v>-25</v>
       </c>
       <c r="C5">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="D5">
         <v>-9</v>
@@ -1157,7 +1157,7 @@
         <v>25</v>
       </c>
       <c r="C18">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="D18">
         <v>25</v>
@@ -1198,7 +1198,7 @@
         <v>-25</v>
       </c>
       <c r="C19">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="D19">
         <v>25</v>
@@ -1239,7 +1239,7 @@
         <v>-25</v>
       </c>
       <c r="C20">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="D20">
         <v>-25</v>
@@ -1280,7 +1280,7 @@
         <v>25</v>
       </c>
       <c r="C21">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="D21">
         <v>-25</v>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1419FEA-AD7A-4236-A51B-6BF4BC0C2B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B0E0B9-F221-4010-AA2C-9905212FF115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33915" yWindow="-300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -580,7 +580,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>2.1</v>
@@ -621,7 +621,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-25</v>
+        <v>-21</v>
       </c>
       <c r="C5">
         <v>2.1</v>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B0E0B9-F221-4010-AA2C-9905212FF115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37777E53-74E0-4F7B-98BA-212F0AD91D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33915" yWindow="-300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -498,7 +498,7 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>2.1</v>
@@ -539,7 +539,7 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="C3">
         <v>2.1</v>
@@ -580,13 +580,13 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>2.1</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -621,13 +621,13 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-21</v>
+        <v>-25</v>
       </c>
       <c r="C5">
         <v>2.1</v>
       </c>
       <c r="D5">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -662,19 +662,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-7.5</v>
+        <v>-14</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="E7">
         <v>0</v>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37777E53-74E0-4F7B-98BA-212F0AD91D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959AC3D7-D990-4912-B87A-C73BE3F1DE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -744,13 +744,13 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -949,19 +949,19 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>-2</v>
+        <v>1.5</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1311,6 +1311,170 @@
       </c>
       <c r="M21">
         <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>-15</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>-90</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>-14</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>0.5</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>5.5</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25">
+        <v>-3.5</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>-3</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>180</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2756559D-9B1E-4425-A29C-65126A745DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846924D0-54C7-4495-9AFC-843355910BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -665,7 +665,7 @@
         <v>-7.5</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>8.5</v>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846924D0-54C7-4495-9AFC-843355910BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A565A3E-0EF8-49DA-8ED5-B13FBB7F5462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -1149,6 +1149,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A565A3E-0EF8-49DA-8ED5-B13FBB7F5462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959AC3D7-D990-4912-B87A-C73BE3F1DE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -498,10 +498,10 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="D2">
         <v>-25</v>
@@ -539,10 +539,10 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>-7.5</v>
+        <v>-7</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -583,10 +583,10 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -624,7 +624,7 @@
         <v>-25</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="D5">
         <v>-7</v>
@@ -662,19 +662,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-7.5</v>
+        <v>-14</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -744,13 +744,13 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -949,19 +949,19 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>-2</v>
+        <v>1.5</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13">
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1151,36 +1151,329 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18">
+        <v>25</v>
+      </c>
+      <c r="C18">
+        <v>2.1</v>
+      </c>
+      <c r="D18">
+        <v>25</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0.5</v>
+      </c>
+      <c r="I18">
+        <v>0.5</v>
+      </c>
+      <c r="J18">
+        <v>0.5</v>
+      </c>
+      <c r="K18">
+        <v>-1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19">
+        <v>-25</v>
+      </c>
+      <c r="C19">
+        <v>2.1</v>
+      </c>
+      <c r="D19">
+        <v>25</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0.5</v>
+      </c>
+      <c r="I19">
+        <v>0.5</v>
+      </c>
+      <c r="J19">
+        <v>0.5</v>
+      </c>
+      <c r="K19">
+        <v>10</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20">
+        <v>-25</v>
+      </c>
+      <c r="C20">
+        <v>2.1</v>
+      </c>
+      <c r="D20">
+        <v>-25</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0.5</v>
+      </c>
+      <c r="I20">
+        <v>0.5</v>
+      </c>
+      <c r="J20">
+        <v>0.5</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>2.1</v>
+      </c>
+      <c r="D21">
+        <v>-25</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0.5</v>
+      </c>
+      <c r="I21">
+        <v>0.5</v>
+      </c>
+      <c r="J21">
+        <v>0.5</v>
+      </c>
+      <c r="K21">
+        <v>-10</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" t="s">
         <v>16</v>
       </c>
-      <c r="C18">
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>2</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
+      <c r="D22">
+        <v>-15</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>-90</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>-14</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>0.5</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>5.5</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25">
+        <v>-3.5</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>-3</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>180</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959AC3D7-D990-4912-B87A-C73BE3F1DE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE49BF0-E251-4B80-9554-0DEA29692F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="780" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -668,7 +668,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -703,13 +703,13 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-12.5</v>
+        <v>-10.5</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -785,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-5.5</v>
+        <v>-1.5</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1359,13 +1359,13 @@
         <v>16</v>
       </c>
       <c r="B23">
-        <v>-14</v>
+        <v>6.5</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23">
-        <v>0.5</v>
+        <v>-3</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1441,13 +1441,13 @@
         <v>16</v>
       </c>
       <c r="B25">
-        <v>-3.5</v>
+        <v>-4</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="E25">
         <v>0</v>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE49BF0-E251-4B80-9554-0DEA29692F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9966459B-5C76-4620-96F9-A10A611B55C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -504,7 +504,7 @@
         <v>2.1</v>
       </c>
       <c r="D2">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="C5">
         <v>2.1</v>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9966459B-5C76-4620-96F9-A10A611B55C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0C9D56-BC3C-4A69-B17C-A035BEBD24AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -665,7 +665,7 @@
         <v>-14</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D6">
         <v>-1</v>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0C9D56-BC3C-4A69-B17C-A035BEBD24AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C0EC2B-5F03-4F31-9924-618C346A9F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5265" yWindow="1575" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -668,7 +668,7 @@
         <v>1.5</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -703,13 +703,13 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-10.5</v>
+        <v>-10</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1474,6 +1474,334 @@
         <v>0</v>
       </c>
       <c r="M25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26">
+        <v>8.5</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>19</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0.5</v>
+      </c>
+      <c r="I26">
+        <v>0.5</v>
+      </c>
+      <c r="J26">
+        <v>0.5</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>19</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0.5</v>
+      </c>
+      <c r="I27">
+        <v>0.5</v>
+      </c>
+      <c r="J27">
+        <v>0.5</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28">
+        <v>-7.3</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>19</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0.5</v>
+      </c>
+      <c r="I28">
+        <v>0.5</v>
+      </c>
+      <c r="J28">
+        <v>0.5</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29">
+        <v>18.5</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>-18.5</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0.5</v>
+      </c>
+      <c r="I29">
+        <v>0.5</v>
+      </c>
+      <c r="J29">
+        <v>0.5</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30">
+        <v>18</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>18.5</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0.5</v>
+      </c>
+      <c r="I30">
+        <v>0.5</v>
+      </c>
+      <c r="J30">
+        <v>0.5</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31">
+        <v>3.5</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>-2</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0.5</v>
+      </c>
+      <c r="I31">
+        <v>0.5</v>
+      </c>
+      <c r="J31">
+        <v>0.5</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32">
+        <v>19</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>-10</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0.5</v>
+      </c>
+      <c r="I32">
+        <v>0.5</v>
+      </c>
+      <c r="J32">
+        <v>0.5</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33">
+        <v>15.3</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>-6</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0.5</v>
+      </c>
+      <c r="I33">
+        <v>0.5</v>
+      </c>
+      <c r="J33">
+        <v>0.5</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C0EC2B-5F03-4F31-9924-618C346A9F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9526EA80-3C8D-49E8-BDA0-BAB6EF433DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5265" yWindow="1575" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7005" yWindow="1140" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -662,13 +662,13 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="C6">
         <v>1.5</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -986,44 +986,8 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14">
-        <v>15</v>
-      </c>
       <c r="C14">
         <v>2</v>
-      </c>
-      <c r="D14">
-        <v>0.5</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>180</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1802,6 +1766,88 @@
         <v>0</v>
       </c>
       <c r="M33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34">
+        <v>-19</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>19</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0.5</v>
+      </c>
+      <c r="I34">
+        <v>0.5</v>
+      </c>
+      <c r="J34">
+        <v>0.5</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35">
+        <v>-18.5</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0.5</v>
+      </c>
+      <c r="I35">
+        <v>0.5</v>
+      </c>
+      <c r="J35">
+        <v>0.5</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9526EA80-3C8D-49E8-BDA0-BAB6EF433DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987F76F4-730A-4E6F-9B45-BB375F4BAB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7005" yWindow="1140" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -986,40 +986,76 @@
       </c>
     </row>
     <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>-1</v>
+      </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0.01</v>
+      </c>
+      <c r="I14">
+        <v>0.01</v>
+      </c>
+      <c r="J14">
+        <v>0.01</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>-7.5</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>20</v>
+        <v>-7</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1033,34 +1069,34 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>-7.5</v>
+        <v>-3</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>-7</v>
+        <v>-10.5</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1074,16 +1110,16 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17">
-        <v>-3</v>
+        <v>25</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="D17">
-        <v>-10.5</v>
+        <v>25</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1104,13 +1140,13 @@
         <v>0.5</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1118,7 +1154,7 @@
         <v>13</v>
       </c>
       <c r="B18">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="C18">
         <v>2.1</v>
@@ -1145,13 +1181,13 @@
         <v>0.5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1165,7 +1201,7 @@
         <v>2.1</v>
       </c>
       <c r="D19">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1186,13 +1222,13 @@
         <v>0.5</v>
       </c>
       <c r="K19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1200,7 +1236,7 @@
         <v>13</v>
       </c>
       <c r="B20">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>2.1</v>
@@ -1227,54 +1263,54 @@
         <v>0.5</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>-25</v>
+        <v>-15</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1282,19 +1318,19 @@
         <v>16</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22">
-        <v>-15</v>
+        <v>-3</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1323,13 +1359,13 @@
         <v>16</v>
       </c>
       <c r="B23">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23">
-        <v>-3</v>
+        <v>5.5</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1364,19 +1400,19 @@
         <v>16</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1402,34 +1438,34 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25">
-        <v>-4</v>
+        <v>8.5</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1446,7 +1482,7 @@
         <v>15</v>
       </c>
       <c r="B26">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1487,7 +1523,7 @@
         <v>15</v>
       </c>
       <c r="B27">
-        <v>12</v>
+        <v>-7.3</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1528,13 +1564,13 @@
         <v>15</v>
       </c>
       <c r="B28">
-        <v>-7.3</v>
+        <v>18.5</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>19</v>
+        <v>-18.5</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1569,13 +1605,13 @@
         <v>15</v>
       </c>
       <c r="B29">
+        <v>18</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
         <v>18.5</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>-18.5</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1610,13 +1646,13 @@
         <v>15</v>
       </c>
       <c r="B30">
-        <v>18</v>
+        <v>3.5</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30">
-        <v>18.5</v>
+        <v>-2</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1651,13 +1687,13 @@
         <v>15</v>
       </c>
       <c r="B31">
-        <v>3.5</v>
+        <v>19</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1692,13 +1728,13 @@
         <v>15</v>
       </c>
       <c r="B32">
-        <v>19</v>
+        <v>15.3</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1733,13 +1769,13 @@
         <v>15</v>
       </c>
       <c r="B33">
-        <v>15.3</v>
+        <v>-19</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>-6</v>
+        <v>19</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1774,13 +1810,13 @@
         <v>15</v>
       </c>
       <c r="B34">
-        <v>-19</v>
+        <v>-18.5</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1807,47 +1843,6 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35">
-        <v>-18.5</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>8</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0.5</v>
-      </c>
-      <c r="I35">
-        <v>0.5</v>
-      </c>
-      <c r="J35">
-        <v>0.5</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987F76F4-730A-4E6F-9B45-BB375F4BAB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591B7EE1-A130-4E86-9310-3181ACE29B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5460" yWindow="795" windowWidth="21600" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -1564,13 +1564,13 @@
         <v>15</v>
       </c>
       <c r="B28">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>-18.5</v>
+        <v>-17</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1605,13 +1605,13 @@
         <v>15</v>
       </c>
       <c r="B29">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1769,13 +1769,13 @@
         <v>15</v>
       </c>
       <c r="B33">
-        <v>-19</v>
+        <v>-17</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1810,7 +1810,7 @@
         <v>15</v>
       </c>
       <c r="B34">
-        <v>-18.5</v>
+        <v>-17</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1843,6 +1843,47 @@
         <v>0</v>
       </c>
       <c r="M34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35">
+        <v>-7</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>-16</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0.5</v>
+      </c>
+      <c r="I35">
+        <v>0.5</v>
+      </c>
+      <c r="J35">
+        <v>0.5</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591B7EE1-A130-4E86-9310-3181ACE29B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C0EC2B-5F03-4F31-9924-618C346A9F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="795" windowWidth="21600" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5265" yWindow="1575" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -662,13 +662,13 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="C6">
         <v>1.5</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -987,34 +987,34 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1028,34 +1028,34 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
-        <v>-7.5</v>
+        <v>-1</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>-7</v>
+        <v>20</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1069,34 +1069,34 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16">
-        <v>-3</v>
+        <v>-7.5</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>-10.5</v>
+        <v>-7</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1110,16 +1110,16 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>25</v>
+        <v>-3</v>
       </c>
       <c r="C17">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>-10.5</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1140,13 +1140,13 @@
         <v>0.5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1154,7 +1154,7 @@
         <v>13</v>
       </c>
       <c r="B18">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>2.1</v>
@@ -1181,13 +1181,13 @@
         <v>0.5</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>-10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1201,7 +1201,7 @@
         <v>2.1</v>
       </c>
       <c r="D19">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1222,13 +1222,13 @@
         <v>0.5</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
       <c r="B20">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="C20">
         <v>2.1</v>
@@ -1263,54 +1263,54 @@
         <v>0.5</v>
       </c>
       <c r="K20">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D21">
-        <v>-15</v>
+        <v>-25</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1318,19 +1318,19 @@
         <v>16</v>
       </c>
       <c r="B22">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22">
-        <v>-3</v>
+        <v>-15</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1359,13 +1359,13 @@
         <v>16</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23">
-        <v>5.5</v>
+        <v>-3</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1400,19 +1400,19 @@
         <v>16</v>
       </c>
       <c r="B24">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1438,34 +1438,34 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25">
-        <v>8.5</v>
+        <v>-4</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1482,7 +1482,7 @@
         <v>15</v>
       </c>
       <c r="B26">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1523,7 +1523,7 @@
         <v>15</v>
       </c>
       <c r="B27">
-        <v>-7.3</v>
+        <v>12</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1564,13 +1564,13 @@
         <v>15</v>
       </c>
       <c r="B28">
-        <v>17</v>
+        <v>-7.3</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>-17</v>
+        <v>19</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1605,13 +1605,13 @@
         <v>15</v>
       </c>
       <c r="B29">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>17</v>
+        <v>-18.5</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1646,13 +1646,13 @@
         <v>15</v>
       </c>
       <c r="B30">
-        <v>3.5</v>
+        <v>18</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30">
-        <v>-2</v>
+        <v>18.5</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1687,13 +1687,13 @@
         <v>15</v>
       </c>
       <c r="B31">
-        <v>19</v>
+        <v>3.5</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1728,13 +1728,13 @@
         <v>15</v>
       </c>
       <c r="B32">
-        <v>15.3</v>
+        <v>19</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1769,13 +1769,13 @@
         <v>15</v>
       </c>
       <c r="B33">
-        <v>-17</v>
+        <v>15.3</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>17</v>
+        <v>-6</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1802,88 +1802,6 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34">
-        <v>-17</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>8</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0.5</v>
-      </c>
-      <c r="I34">
-        <v>0.5</v>
-      </c>
-      <c r="J34">
-        <v>0.5</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35">
-        <v>-7</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>-16</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0.5</v>
-      </c>
-      <c r="I35">
-        <v>0.5</v>
-      </c>
-      <c r="J35">
-        <v>0.5</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C0EC2B-5F03-4F31-9924-618C346A9F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9562919A-04D6-43EB-B3A6-83A2086C4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5265" yWindow="1575" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1441,7 +1441,7 @@
         <v>16</v>
       </c>
       <c r="B25">
-        <v>-4</v>
+        <v>-5.5</v>
       </c>
       <c r="C25">
         <v>2</v>

--- a/Data/Excel/stage3.xlsx
+++ b/Data/Excel/stage3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9562919A-04D6-43EB-B3A6-83A2086C4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36FA090-1B59-47A9-8213-9B8FE3E82AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="15" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="19">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -97,6 +97,9 @@
   <si>
     <t>Goal</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stairs</t>
   </si>
 </sst>
 </file>
@@ -445,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -1453,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1802,6 +1805,88 @@
         <v>0</v>
       </c>
       <c r="M33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34">
+        <v>-14.5</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>0.5</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0.5</v>
+      </c>
+      <c r="I34">
+        <v>0.5</v>
+      </c>
+      <c r="J34">
+        <v>0.5</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35">
+        <v>-14.5</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>-2</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>180</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0.5</v>
+      </c>
+      <c r="I35">
+        <v>0.5</v>
+      </c>
+      <c r="J35">
+        <v>0.5</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
         <v>0</v>
       </c>
     </row>
